--- a/sample-data/don-hang-pos-cua-hang.xlsx
+++ b/sample-data/don-hang-pos-cua-hang.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Đơn POS" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:I30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,13 +421,19 @@
       <c r="G1" t="str">
         <v>Thương hiệu</v>
       </c>
+      <c r="H1" t="str">
+        <v>Trạng thái</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Kênh</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>POS-2025-001</v>
       </c>
       <c r="B2" t="str">
-        <v>01/07/2025</v>
+        <v>2025-07-01 10:15:00</v>
       </c>
       <c r="C2" t="str">
         <v>Đắc Nhân Tâm</v>
@@ -435,14 +441,20 @@
       <c r="D2" t="str">
         <v>9786045678901</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="str">
         <v>2</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
         <v>86000</v>
       </c>
       <c r="G2" t="str">
-        <v>First News</v>
+        <v>NXB Trẻ</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I2" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="3">
@@ -450,7 +462,7 @@
         <v>POS-2025-002</v>
       </c>
       <c r="B3" t="str">
-        <v>02/07/2025</v>
+        <v>2025-07-01 11:30:00</v>
       </c>
       <c r="C3" t="str">
         <v>Nhà Giả Kim</v>
@@ -458,14 +470,20 @@
       <c r="D3" t="str">
         <v>9786045678902</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+      <c r="E3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
         <v>79000</v>
       </c>
       <c r="G3" t="str">
-        <v>Nhã Nam</v>
+        <v>NXB Trẻ</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Tai quay</v>
       </c>
     </row>
     <row r="4">
@@ -473,22 +491,28 @@
         <v>POS-2025-003</v>
       </c>
       <c r="B4" t="str">
-        <v>02/07/2025</v>
+        <v>2025-07-02 09:20:00</v>
       </c>
       <c r="C4" t="str">
         <v>Tuổi Trẻ Đáng Giá Bao Nhiêu</v>
       </c>
       <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
+        <v>9786045678903</v>
+      </c>
+      <c r="E4" t="str">
+        <v>3</v>
+      </c>
+      <c r="F4" t="str">
         <v>90000</v>
       </c>
       <c r="G4" t="str">
-        <v>Nhã Nam</v>
+        <v>NXB Hội Nhà Văn</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Cua hang</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +520,7 @@
         <v>POS-2025-004</v>
       </c>
       <c r="B5" t="str">
-        <v>03/07/2025</v>
+        <v>2025-07-02 14:45:00</v>
       </c>
       <c r="C5" t="str">
         <v>Cà Phê Cùng Tony</v>
@@ -504,14 +528,20 @@
       <c r="D5" t="str">
         <v>9786045678904</v>
       </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
+      <c r="E5" t="str">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
         <v>0</v>
       </c>
       <c r="G5" t="str">
         <v>NXB Trẻ</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I5" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="6">
@@ -519,7 +549,7 @@
         <v>POS-2025-005</v>
       </c>
       <c r="B6" t="str">
-        <v>03/07/2025</v>
+        <v>2025-07-03 16:10:00</v>
       </c>
       <c r="C6" t="str">
         <v>Tôi Thấy Hoa Vàng Trên Cỏ Xanh</v>
@@ -527,175 +557,223 @@
       <c r="D6" t="str">
         <v>9786045678905</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
+      <c r="E6" t="str">
+        <v>1</v>
+      </c>
+      <c r="F6" t="str">
         <v>125000</v>
       </c>
       <c r="G6" t="str">
         <v>NXB Trẻ</v>
       </c>
+      <c r="H6" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I6" t="str">
+        <v>POS</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>POS-2025-006</v>
+        <v>POS-2025-005</v>
       </c>
       <c r="B7" t="str">
-        <v>04/07/2025</v>
+        <v>2025-07-03 16:15:00</v>
       </c>
       <c r="C7" t="str">
-        <v>Dac Nhan Tam</v>
+        <v>Tôi Thấy Hoa Vàng Trên Cỏ Xanh</v>
       </c>
       <c r="D7" t="str">
-        <v>9786045678901</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>86000</v>
+        <v>9786045678905</v>
+      </c>
+      <c r="E7" t="str">
+        <v>1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>125000</v>
       </c>
       <c r="G7" t="str">
-        <v>First News</v>
+        <v>NXB Trẻ</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I7" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>POS-2025-007</v>
+        <v>POS-2025-006</v>
       </c>
       <c r="B8" t="str">
-        <v>04/07/2025</v>
+        <v>15-07-2025 08:30:00</v>
       </c>
       <c r="C8" t="str">
-        <v>Mắt Biếc</v>
+        <v>Đời Thay Đổi Khi Chúng Ta Thay Đổi</v>
       </c>
       <c r="D8" t="str">
         <v>9786045678906</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="str">
         <v>2</v>
       </c>
-      <c r="F8">
-        <v>110000</v>
+      <c r="F8" t="str">
+        <v>68000</v>
       </c>
       <c r="G8" t="str">
         <v>NXB Trẻ</v>
       </c>
+      <c r="H8" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I8" t="str">
+        <v>POS</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>POS-2025-008</v>
+        <v>POS-2025-007</v>
       </c>
       <c r="B9" t="str">
-        <v>05/07/2025</v>
+        <v>2025-07-04 10:00:00</v>
       </c>
       <c r="C9" t="str">
-        <v>Khéo Ăn Nói Sẽ Có Được Thiên Hạ</v>
+        <v>Cha Giàu Cha Nghèo</v>
       </c>
       <c r="D9" t="str">
-        <v>9786045678907</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>110000</v>
+        <v>978-604-5678907</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>115000</v>
       </c>
       <c r="G9" t="str">
-        <v>Minh Long Book</v>
+        <v>NXB Trẻ</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I9" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>POS-2025-009</v>
+        <v>POS-2025-008</v>
       </c>
       <c r="B10" t="str">
-        <v>05/07/2025</v>
+        <v>2025-07-04 11:20:00</v>
       </c>
       <c r="C10" t="str">
-        <v>Đời Thay Đổi Khi Chúng Ta Thay Đổi</v>
+        <v>Đọc Vị Bất Kỳ Ai</v>
       </c>
       <c r="D10" t="str">
         <v>9786045678908</v>
       </c>
-      <c r="E10">
-        <v>4</v>
-      </c>
-      <c r="F10">
-        <v>75000</v>
+      <c r="E10" t="str">
+        <v>1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>89000</v>
       </c>
       <c r="G10" t="str">
-        <v>NXB Trẻ</v>
+        <v>NXB Thế Giới</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I10" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>POS-2025-010</v>
+        <v>POS-2025-009</v>
       </c>
       <c r="B11" t="str">
-        <v>06/07/2025</v>
+        <v>2025-07-05 13:15:00</v>
       </c>
       <c r="C11" t="str">
-        <v>Cha Giàu Cha Nghèo</v>
+        <v>Mắt Biếc</v>
       </c>
       <c r="D11" t="str">
         <v>9786045678909</v>
       </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>135000</v>
+      <c r="E11" t="str">
+        <v>2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>110000</v>
       </c>
       <c r="G11" t="str">
-        <v>Alpha Books</v>
+        <v>NXB Trẻ</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I11" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>POS-2025-011</v>
+        <v>POS-2025-010</v>
       </c>
       <c r="B12" t="str">
-        <v>06/07/2025</v>
+        <v>2025-07-05 15:40:00</v>
       </c>
       <c r="C12" t="str">
-        <v>Tư Duy Nhanh Và Chậm</v>
+        <v>Số Đỏ</v>
       </c>
       <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>220000</v>
+        <v>9786045678910</v>
+      </c>
+      <c r="E12" t="str">
+        <v>5</v>
+      </c>
+      <c r="F12" t="str">
+        <v>65000</v>
       </c>
       <c r="G12" t="str">
-        <v>Alpha Books</v>
+        <v>NXB Văn Học</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I12" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>POS-2025-005</v>
+        <v>POS-2025-011</v>
       </c>
       <c r="B13" t="str">
-        <v>07/07/2025</v>
+        <v>2025-07-06 09:10:00</v>
       </c>
       <c r="C13" t="str">
-        <v>Tôi Thấy Hoa Vàng Trên Cỏ Xanh</v>
+        <v>Tư Duy Nhanh Và Chậm</v>
       </c>
       <c r="D13" t="str">
-        <v>9786045678905</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>125000</v>
+        <v>9786045678911</v>
+      </c>
+      <c r="E13" t="str">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>210000</v>
       </c>
       <c r="G13" t="str">
-        <v>NXB Trẻ</v>
+        <v>NXB Thế Giới</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I13" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="14">
@@ -703,22 +781,28 @@
         <v>POS-2025-012</v>
       </c>
       <c r="B14" t="str">
-        <v>07/07/2025</v>
+        <v>2025-07-06 14:25:00</v>
       </c>
       <c r="C14" t="str">
-        <v>Người Giàu Có Nhất Thành Babylon</v>
+        <v>Khéo Ăn Nói Sẽ Có Được Thiên Hạ</v>
       </c>
       <c r="D14" t="str">
-        <v>9786045678911</v>
-      </c>
-      <c r="E14">
+        <v>9786045678912</v>
+      </c>
+      <c r="E14" t="str">
         <v>2</v>
       </c>
-      <c r="F14">
-        <v>98000</v>
+      <c r="F14" t="str">
+        <v>118000</v>
       </c>
       <c r="G14" t="str">
-        <v>First News</v>
+        <v>NXB Văn Học</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I14" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="15">
@@ -726,22 +810,28 @@
         <v>POS-2025-013</v>
       </c>
       <c r="B15" t="str">
-        <v>08/07/2025</v>
+        <v>2025-07-07 10:50:00</v>
       </c>
       <c r="C15" t="str">
-        <v>Sức Mạnh Của Hiện Tại</v>
+        <v>Dế Mèn Phiêu Lưu Ký</v>
       </c>
       <c r="D15" t="str">
-        <v>9786045678912</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>130000</v>
+        <v>9786045678913</v>
+      </c>
+      <c r="E15" t="str">
+        <v>4</v>
+      </c>
+      <c r="F15" t="str">
+        <v>55000</v>
       </c>
       <c r="G15" t="str">
-        <v>First News</v>
+        <v>NXB Kim Đồng</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I15" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="16">
@@ -749,22 +839,28 @@
         <v>POS-2025-014</v>
       </c>
       <c r="B16" t="str">
-        <v>15-07-2025</v>
+        <v>2025-07-07 16:30:00</v>
       </c>
       <c r="C16" t="str">
-        <v>Đi Tìm Lẽ Sống</v>
+        <v>Chiếc Thuyền Ngoài Xa</v>
       </c>
       <c r="D16" t="str">
-        <v>9786045678913</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>88000</v>
+        <v>9786045678914</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1</v>
+      </c>
+      <c r="F16" t="str">
+        <v>48000</v>
       </c>
       <c r="G16" t="str">
-        <v>First News</v>
+        <v>NXB Văn Học</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I16" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="17">
@@ -772,22 +868,28 @@
         <v>POS-2025-015</v>
       </c>
       <c r="B17" t="str">
-        <v>09/07/2025</v>
+        <v>2025-07-08 11:05:00</v>
       </c>
       <c r="C17" t="str">
-        <v>Đọc Vị Bất Kỳ Ai</v>
+        <v>Tắt Đèn</v>
       </c>
       <c r="D17" t="str">
-        <v>9786045678914</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17">
-        <v>89000</v>
+        <v>9786045678915</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2</v>
+      </c>
+      <c r="F17" t="str">
+        <v>52000</v>
       </c>
       <c r="G17" t="str">
-        <v>Alpha Books</v>
+        <v>NXB Văn Học</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I17" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="18">
@@ -795,22 +897,28 @@
         <v>POS-2025-016</v>
       </c>
       <c r="B18" t="str">
-        <v>10/07/2025</v>
+        <v>2025-07-08 15:20:00</v>
       </c>
       <c r="C18" t="str">
-        <v>Lược Sử Loài Người</v>
+        <v>Lão Hạc</v>
       </c>
       <c r="D18" t="str">
-        <v>9786045678915</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>240000</v>
+        <v>9786045678916</v>
+      </c>
+      <c r="E18" t="str">
+        <v>3</v>
+      </c>
+      <c r="F18" t="str">
+        <v>45000</v>
       </c>
       <c r="G18" t="str">
-        <v>Nhã Nam</v>
+        <v>NXB Văn Học</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I18" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="19">
@@ -818,22 +926,28 @@
         <v>POS-2025-017</v>
       </c>
       <c r="B19" t="str">
-        <v>10/07/2025</v>
+        <v>2025-07-09 09:40:00</v>
       </c>
       <c r="C19" t="str">
-        <v>Hạt Giống Tâm Hồn</v>
+        <v>Vợ Nhặt</v>
       </c>
       <c r="D19" t="str">
-        <v>9786045678916</v>
-      </c>
-      <c r="E19">
+        <v>9786045678917</v>
+      </c>
+      <c r="E19" t="str">
         <v>2</v>
       </c>
-      <c r="F19">
-        <v>68000</v>
+      <c r="F19" t="str">
+        <v>42000</v>
       </c>
       <c r="G19" t="str">
-        <v>First News</v>
+        <v>NXB Văn Học</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I19" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="20">
@@ -841,22 +955,28 @@
         <v>POS-2025-018</v>
       </c>
       <c r="B20" t="str">
-        <v>11/07/2025</v>
+        <v>2025-07-09 14:15:00</v>
       </c>
       <c r="C20" t="str">
-        <v>Số Đỏ</v>
+        <v>Hạt Giống Tâm Hồn</v>
       </c>
       <c r="D20" t="str">
-        <v>9786045678917</v>
-      </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
-      <c r="F20">
-        <v>65000</v>
+        <v>9786045678918</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>75000</v>
       </c>
       <c r="G20" t="str">
-        <v>Nhã Nam</v>
+        <v>NXB Tổng Hợp TP.HCM</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I20" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="21">
@@ -864,22 +984,28 @@
         <v>POS-2025-019</v>
       </c>
       <c r="B21" t="str">
-        <v>11/07/2025</v>
+        <v>2025-07-10 10:30:00</v>
       </c>
       <c r="C21" t="str">
-        <v>Tắt Đèn</v>
+        <v>Sức Mạnh Của Hiện Tại</v>
       </c>
       <c r="D21" t="str">
-        <v>9786045678918</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>55000</v>
+        <v>9786045678919</v>
+      </c>
+      <c r="E21" t="str">
+        <v>1</v>
+      </c>
+      <c r="F21" t="str">
+        <v>135000</v>
       </c>
       <c r="G21" t="str">
-        <v>Kim Đồng</v>
+        <v>NXB Tổng Hợp TP.HCM</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I21" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="22">
@@ -887,22 +1013,28 @@
         <v>POS-2025-020</v>
       </c>
       <c r="B22" t="str">
-        <v>12/07/2025</v>
+        <v>2025-07-10 16:00:00</v>
       </c>
       <c r="C22" t="str">
-        <v>Rừng Na Uy</v>
+        <v>Đắc Nhân Tâm</v>
       </c>
       <c r="D22" t="str">
-        <v>9786045678919</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>145000</v>
+        <v>9786045678901</v>
+      </c>
+      <c r="E22" t="str">
+        <v>1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>86000</v>
       </c>
       <c r="G22" t="str">
-        <v>Nhã Nam</v>
+        <v>NXB Trẻ</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I22" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="23">
@@ -910,22 +1042,28 @@
         <v>POS-2025-021</v>
       </c>
       <c r="B23" t="str">
-        <v>12/07/2025</v>
+        <v>2025-07-11 11:45:00</v>
       </c>
       <c r="C23" t="str">
-        <v>Thế Giới Quả Là Rộng Lớn Và Có Nhiều Việc Phải Làm</v>
+        <v>Nhà Giả Kim (bản đặc biệt)</v>
       </c>
       <c r="D23" t="str">
-        <v>9786045678920</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>105000</v>
+        <v>9786045678902</v>
+      </c>
+      <c r="E23" t="str">
+        <v>1</v>
+      </c>
+      <c r="F23" t="str">
+        <v>79000</v>
       </c>
       <c r="G23" t="str">
-        <v>NXB Trẻ</v>
+        <v>NXB Nhã Nam</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I23" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="24">
@@ -933,22 +1071,28 @@
         <v>POS-2025-022</v>
       </c>
       <c r="B24" t="str">
-        <v>13/07/2025</v>
+        <v>2025-07-11 15:10:00</v>
       </c>
       <c r="C24" t="str">
-        <v>Đắc Nhân Tâm</v>
+        <v>Cha Giàu Cha Nghèo</v>
       </c>
       <c r="D24" t="str">
-        <v>9786045678901</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>86000</v>
+        <v>9786045678907</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2</v>
+      </c>
+      <c r="F24" t="str">
+        <v>115000</v>
       </c>
       <c r="G24" t="str">
-        <v>First News</v>
+        <v>NXB Trẻ</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I24" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="25">
@@ -956,22 +1100,28 @@
         <v>POS-2025-023</v>
       </c>
       <c r="B25" t="str">
-        <v>13/07/2025</v>
+        <v>2025-07-12 09:30:00</v>
       </c>
       <c r="C25" t="str">
-        <v>Nhà Giả Kim</v>
+        <v>Số Đỏ</v>
       </c>
       <c r="D25" t="str">
-        <v>9786045678902</v>
-      </c>
-      <c r="E25">
-        <v>3</v>
-      </c>
-      <c r="F25">
-        <v>79000</v>
+        <v>9786045678910</v>
+      </c>
+      <c r="E25" t="str">
+        <v>4</v>
+      </c>
+      <c r="F25" t="str">
+        <v>65000</v>
       </c>
       <c r="G25" t="str">
-        <v>Nhã Nam</v>
+        <v>NXB Văn Học</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I25" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="26">
@@ -979,22 +1129,28 @@
         <v>POS-2025-024</v>
       </c>
       <c r="B26" t="str">
-        <v>14/07/2025</v>
+        <v>2025-07-12 14:00:00</v>
       </c>
       <c r="C26" t="str">
-        <v>Tuổi Trẻ Đáng Giá Bao Nhiêu</v>
+        <v>Mắt Biếc</v>
       </c>
       <c r="D26" t="str">
-        <v>9786045678903</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26">
-        <v>90000</v>
+        <v>9786045678909</v>
+      </c>
+      <c r="E26" t="str">
+        <v>1</v>
+      </c>
+      <c r="F26" t="str">
+        <v>110000</v>
       </c>
       <c r="G26" t="str">
-        <v>Nhã Nam</v>
+        <v>NXB Trẻ</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I26" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="27">
@@ -1002,22 +1158,28 @@
         <v>POS-2025-025</v>
       </c>
       <c r="B27" t="str">
-        <v>14/07/2025</v>
+        <v>2025-07-13 10:20:00</v>
       </c>
       <c r="C27" t="str">
-        <v>Mắt Biếc</v>
+        <v>Đắc Nhân Tâm</v>
       </c>
       <c r="D27" t="str">
-        <v>9786045678906</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>110000</v>
+        <v>9786045678999</v>
+      </c>
+      <c r="E27" t="str">
+        <v>1</v>
+      </c>
+      <c r="F27" t="str">
+        <v>86000</v>
       </c>
       <c r="G27" t="str">
         <v>NXB Trẻ</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I27" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="28">
@@ -1025,22 +1187,28 @@
         <v>POS-2025-026</v>
       </c>
       <c r="B28" t="str">
-        <v>15/07/2025</v>
+        <v>2025-07-13 16:45:00</v>
       </c>
       <c r="C28" t="str">
-        <v>Cha Giàu Cha Nghèo</v>
+        <v>Tuổi Trẻ Đáng Giá Bao Nhiêu</v>
       </c>
       <c r="D28" t="str">
-        <v>9786045678909</v>
-      </c>
-      <c r="E28">
+        <v>9786045678903</v>
+      </c>
+      <c r="E28" t="str">
         <v>2</v>
       </c>
-      <c r="F28">
-        <v>135000</v>
+      <c r="F28" t="str">
+        <v>90000</v>
       </c>
       <c r="G28" t="str">
-        <v>Alpha Books</v>
+        <v>NXB Hội Nhà Văn</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I28" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="29">
@@ -1048,22 +1216,28 @@
         <v>POS-2025-027</v>
       </c>
       <c r="B29" t="str">
-        <v>16/07/2025</v>
+        <v>2025-07-14 11:15:00</v>
       </c>
       <c r="C29" t="str">
-        <v>Sức Mạnh Của Hiện Tại</v>
+        <v>Sách Giáo Khoa Toán 12</v>
       </c>
       <c r="D29" t="str">
-        <v>9786045678912</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>130000</v>
+        <v>9789999999999</v>
+      </c>
+      <c r="E29" t="str">
+        <v>1</v>
+      </c>
+      <c r="F29" t="str">
+        <v>35000</v>
       </c>
       <c r="G29" t="str">
-        <v>First News</v>
+        <v>NXB Giáo Dục</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Đã hủy</v>
+      </c>
+      <c r="I29" t="str">
+        <v>POS</v>
       </c>
     </row>
     <row r="30">
@@ -1071,50 +1245,33 @@
         <v>POS-2025-028</v>
       </c>
       <c r="B30" t="str">
-        <v>16/07/2025</v>
+        <v>2025-07-14 15:30:00</v>
       </c>
       <c r="C30" t="str">
-        <v>Lược Sử Loài Người</v>
+        <v>Cà Phê Cùng Tony</v>
       </c>
       <c r="D30" t="str">
-        <v>9786045678915</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>240000</v>
+        <v>9786045678904</v>
+      </c>
+      <c r="E30" t="str">
+        <v>1</v>
+      </c>
+      <c r="F30" t="str">
+        <v>95000</v>
       </c>
       <c r="G30" t="str">
-        <v>Nhã Nam</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>POS-2025-029</v>
-      </c>
-      <c r="B31" t="str">
-        <v>17/07/2025</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Rừng Na Uy</v>
-      </c>
-      <c r="D31" t="str">
-        <v>9786045678919</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>145000</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Nhã Nam</v>
+        <v>NXB Trẻ</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I30" t="str">
+        <v>POS</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I30"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample-data/don-hang-pos-cua-hang.xlsx
+++ b/sample-data/don-hang-pos-cua-hang.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Đơn POS" sheetId="1" r:id="rId1"/>
+    <sheet name="Đơn POS Đa Ngành" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,7 +410,7 @@
         <v>Tên sản phẩm</v>
       </c>
       <c r="D1" t="str">
-        <v>ISBN</v>
+        <v>Mã vạch / SKU</v>
       </c>
       <c r="E1" t="str">
         <v>Số lượng</v>
@@ -523,19 +523,19 @@
         <v>2025-07-02 14:45:00</v>
       </c>
       <c r="C5" t="str">
-        <v>Tuổi Trẻ Đáng Giá Bao Nhiêu</v>
+        <v>Áo Thun Nam Cotton Compact</v>
       </c>
       <c r="D5" t="str">
-        <v>9786045678903</v>
+        <v>8935001234567</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="G5" t="str">
-        <v>NXB Hội Nhà Văn</v>
+        <v>Coolmate</v>
       </c>
       <c r="H5" t="str">
         <v>Hoàn thành</v>
@@ -552,19 +552,19 @@
         <v>2025-07-03 16:10:00</v>
       </c>
       <c r="C6" t="str">
-        <v>Cà Phê Cùng Tony</v>
+        <v>Quần Jean Nam Slimfit</v>
       </c>
       <c r="D6" t="str">
-        <v>9786045678904</v>
+        <v>8935001234568</v>
       </c>
       <c r="E6" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>95000</v>
+        <v>449000</v>
       </c>
       <c r="G6" t="str">
-        <v>NXB Trẻ</v>
+        <v>Canifa</v>
       </c>
       <c r="H6" t="str">
         <v>Hoàn thành</v>
@@ -581,19 +581,19 @@
         <v>2025-07-03 16:15:00</v>
       </c>
       <c r="C7" t="str">
-        <v>Cà Phê Cùng Tony</v>
+        <v>Quần Jean Nam Slimfit</v>
       </c>
       <c r="D7" t="str">
-        <v>9786045678904</v>
+        <v>8935001234568</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>95000</v>
+        <v>449000</v>
       </c>
       <c r="G7" t="str">
-        <v>NXB Trẻ</v>
+        <v>Canifa</v>
       </c>
       <c r="H7" t="str">
         <v>Hoàn thành</v>
@@ -610,19 +610,19 @@
         <v>15-07-2025 08:30:00</v>
       </c>
       <c r="C8" t="str">
-        <v>Tôi Thấy Hoa Vàng Trên Cỏ Xanh</v>
+        <v>Giày Thể Thao Biti's Hunter Street</v>
       </c>
       <c r="D8" t="str">
-        <v>9786045678905</v>
+        <v>8935001234569</v>
       </c>
       <c r="E8" t="str">
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>125000</v>
+        <v>899000</v>
       </c>
       <c r="G8" t="str">
-        <v>NXB Trẻ</v>
+        <v>Biti's</v>
       </c>
       <c r="H8" t="str">
         <v>Hoàn thành</v>
@@ -639,19 +639,19 @@
         <v>2025-07-04 10:00:00</v>
       </c>
       <c r="C9" t="str">
-        <v>Dế Mèn Phiêu Lưu Ký</v>
+        <v>Nồi Chiên Không Dầu Philips 4.5L</v>
       </c>
       <c r="D9" t="str">
-        <v>9786045678913</v>
+        <v>8710103856789</v>
       </c>
       <c r="E9" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>55000</v>
+        <v>1490000</v>
       </c>
       <c r="G9" t="str">
-        <v>NXB Kim Đồng</v>
+        <v>Philips</v>
       </c>
       <c r="H9" t="str">
         <v>Hoàn thành</v>
@@ -668,30 +668,146 @@
         <v>2025-07-04 11:20:00</v>
       </c>
       <c r="C10" t="str">
-        <v>Sách Giáo Khoa Toán 12</v>
+        <v>Ấm Siêu Tốc Inox Sunhouse 1.8L</v>
       </c>
       <c r="D10" t="str">
-        <v>9789999999999</v>
+        <v>8935001234570</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="G10" t="str">
-        <v>NXB Giáo Dục</v>
+        <v>Sunhouse</v>
       </c>
       <c r="H10" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I10" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>POS-2025-009</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2025-07-05 13:15:00</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Tai Nghe Bluetooth Xiaomi Redmi Buds 4</v>
+      </c>
+      <c r="D11" t="str">
+        <v>6934177785678</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>490000</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Xiaomi</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I11" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>POS-2025-010</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2025-07-05 15:40:00</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Kem Chống Nắng La Roche-Posay Anthelios</v>
+      </c>
+      <c r="D12" t="str">
+        <v>3337875591079</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>395000</v>
+      </c>
+      <c r="G12" t="str">
+        <v>La Roche-Posay</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I12" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>POS-2025-011</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2025-07-06 09:10:00</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Nước Tẩy Trang Bí Đao Cocoon 500ml</v>
+      </c>
+      <c r="D13" t="str">
+        <v>8936173200123</v>
+      </c>
+      <c r="E13" t="str">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>245000</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Cocoon</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I13" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>POS-2025-012</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2025-07-06 14:25:00</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Sữa Rửa Mặt CeraVe Foaming Cleanser 236ml</v>
+      </c>
+      <c r="D14" t="str">
+        <v>3337875597354</v>
+      </c>
+      <c r="E14" t="str">
+        <v>1</v>
+      </c>
+      <c r="F14" t="str">
+        <v>320000</v>
+      </c>
+      <c r="G14" t="str">
+        <v>CeraVe</v>
+      </c>
+      <c r="H14" t="str">
         <v>Đã hủy</v>
       </c>
-      <c r="I10" t="str">
+      <c r="I14" t="str">
         <v>POS</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample-data/don-hang-pos-cua-hang.xlsx
+++ b/sample-data/don-hang-pos-cua-hang.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Đơn POS Đa Ngành" sheetId="1" r:id="rId1"/>
+    <sheet name="Đơn POS Tại Quầy" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,7 +436,7 @@
         <v>2025-07-01 10:15:00</v>
       </c>
       <c r="C2" t="str">
-        <v>Mãi mãi tuổi hai mươi (Độc quyền - Bìa cứng)</v>
+        <v>Mãi Mãi Tuổi Hai Mươi (Độc Quyền - Bìa Cứng)</v>
       </c>
       <c r="D2" t="str">
         <v>9786042392440</v>
@@ -465,7 +465,7 @@
         <v>2025-07-01 11:30:00</v>
       </c>
       <c r="C3" t="str">
-        <v>Đắc Nhân Tâm</v>
+        <v>Đắc Nhân Tâm (Tái Bản 2025)</v>
       </c>
       <c r="D3" t="str">
         <v>9786045678901</v>
@@ -483,7 +483,7 @@
         <v>Hoàn thành</v>
       </c>
       <c r="I3" t="str">
-        <v>Tai quay</v>
+        <v>Tại quầy</v>
       </c>
     </row>
     <row r="4">
@@ -520,22 +520,22 @@
         <v>POS-2025-004</v>
       </c>
       <c r="B5" t="str">
-        <v>2025-07-02 14:45:00</v>
+        <v>02/07/2025 14:00:00</v>
       </c>
       <c r="C5" t="str">
-        <v>Áo Thun Nam Cotton Compact</v>
+        <v>Tuổi Trẻ Đáng Giá Bao Nhiêu</v>
       </c>
       <c r="D5" t="str">
-        <v>8935001234567</v>
+        <v>9786045678903</v>
       </c>
       <c r="E5" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>199000</v>
+        <v>90000</v>
       </c>
       <c r="G5" t="str">
-        <v>Coolmate</v>
+        <v>NXB Hội Nhà Văn</v>
       </c>
       <c r="H5" t="str">
         <v>Hoàn thành</v>
@@ -549,22 +549,22 @@
         <v>POS-2025-005</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-07-03 16:10:00</v>
+        <v>2025-07-03 08:45:00</v>
       </c>
       <c r="C6" t="str">
-        <v>Quần Jean Nam Slimfit</v>
+        <v>Cà Phê Cùng Tony</v>
       </c>
       <c r="D6" t="str">
-        <v>8935001234568</v>
+        <v>9786045678904</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>449000</v>
+        <v>72000</v>
       </c>
       <c r="G6" t="str">
-        <v>Canifa</v>
+        <v>NXB Trẻ</v>
       </c>
       <c r="H6" t="str">
         <v>Hoàn thành</v>
@@ -575,25 +575,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>POS-2025-005</v>
+        <v>POS-2025-006</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-07-03 16:15:00</v>
+        <v>2025-07-03 10:30:00</v>
       </c>
       <c r="C7" t="str">
-        <v>Quần Jean Nam Slimfit</v>
+        <v>Tôi Thấy Hoa Vàng Trên Cỏ Xanh</v>
       </c>
       <c r="D7" t="str">
-        <v>8935001234568</v>
+        <v>9786045678905</v>
       </c>
       <c r="E7" t="str">
         <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>449000</v>
+        <v>85000</v>
       </c>
       <c r="G7" t="str">
-        <v>Canifa</v>
+        <v>NXB Trẻ</v>
       </c>
       <c r="H7" t="str">
         <v>Hoàn thành</v>
@@ -604,25 +604,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>POS-2025-006</v>
+        <v>POS-2025-007</v>
       </c>
       <c r="B8" t="str">
-        <v>15-07-2025 08:30:00</v>
+        <v>2025-07-04 09:00:00</v>
       </c>
       <c r="C8" t="str">
-        <v>Giày Thể Thao Biti's Hunter Street</v>
+        <v>Cho Tôi Xin Một Vé Đi Tuổi Thơ</v>
       </c>
       <c r="D8" t="str">
-        <v>8935001234569</v>
+        <v>9786045678906</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>899000</v>
+        <v>65000</v>
       </c>
       <c r="G8" t="str">
-        <v>Biti's</v>
+        <v>NXB Trẻ</v>
       </c>
       <c r="H8" t="str">
         <v>Hoàn thành</v>
@@ -633,25 +633,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>POS-2025-007</v>
+        <v>POS-2025-008</v>
       </c>
       <c r="B9" t="str">
-        <v>2025-07-04 10:00:00</v>
+        <v>2025-07-04 11:15:00</v>
       </c>
       <c r="C9" t="str">
-        <v>Nồi Chiên Không Dầu Philips 4.5L</v>
+        <v>Sapiens: Lược Sử Loài Người</v>
       </c>
       <c r="D9" t="str">
-        <v>8710103856789</v>
+        <v>9786045678907</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>1490000</v>
+        <v>189000</v>
       </c>
       <c r="G9" t="str">
-        <v>Philips</v>
+        <v>NXB Thế Giới</v>
       </c>
       <c r="H9" t="str">
         <v>Hoàn thành</v>
@@ -662,25 +662,25 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>POS-2025-008</v>
+        <v>POS-2025-009</v>
       </c>
       <c r="B10" t="str">
-        <v>2025-07-04 11:20:00</v>
+        <v>15-07-2025 08:30:00</v>
       </c>
       <c r="C10" t="str">
-        <v>Ấm Siêu Tốc Inox Sunhouse 1.8L</v>
+        <v>Atomic Habits - Thay Đổi Tí Hon Hiệu Quả Bất Ngờ</v>
       </c>
       <c r="D10" t="str">
-        <v>8935001234570</v>
+        <v>9786045678908</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>0</v>
+        <v>149000</v>
       </c>
       <c r="G10" t="str">
-        <v>Sunhouse</v>
+        <v>NXB Thế Giới</v>
       </c>
       <c r="H10" t="str">
         <v>Hoàn thành</v>
@@ -691,25 +691,25 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>POS-2025-009</v>
+        <v>POS-2025-010</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-07-05 13:15:00</v>
+        <v>2025-07-05 14:20:00</v>
       </c>
       <c r="C11" t="str">
-        <v>Tai Nghe Bluetooth Xiaomi Redmi Buds 4</v>
+        <v>Dám Bị Ghét</v>
       </c>
       <c r="D11" t="str">
-        <v>6934177785678</v>
+        <v>9786045678909</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>490000</v>
+        <v>115000</v>
       </c>
       <c r="G11" t="str">
-        <v>Xiaomi</v>
+        <v>NXB Lao Động</v>
       </c>
       <c r="H11" t="str">
         <v>Hoàn thành</v>
@@ -720,25 +720,25 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>POS-2025-010</v>
+        <v>POS-2025-011</v>
       </c>
       <c r="B12" t="str">
-        <v>2025-07-05 15:40:00</v>
+        <v>2025-07-06 09:00:00</v>
       </c>
       <c r="C12" t="str">
-        <v>Kem Chống Nắng La Roche-Posay Anthelios</v>
+        <v>Áo Thun Nam Cotton Compact Cổ Tròn</v>
       </c>
       <c r="D12" t="str">
-        <v>3337875591079</v>
+        <v>8935001234567</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="str">
-        <v>395000</v>
+        <v>199000</v>
       </c>
       <c r="G12" t="str">
-        <v>La Roche-Posay</v>
+        <v>Coolmate</v>
       </c>
       <c r="H12" t="str">
         <v>Hoàn thành</v>
@@ -749,25 +749,25 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>POS-2025-011</v>
+        <v>POS-2025-012</v>
       </c>
       <c r="B13" t="str">
-        <v>2025-07-06 09:10:00</v>
+        <v>2025-07-06 10:30:00</v>
       </c>
       <c r="C13" t="str">
-        <v>Nước Tẩy Trang Bí Đao Cocoon 500ml</v>
+        <v>Quần Jean Nam Slimfit Co Giãn</v>
       </c>
       <c r="D13" t="str">
-        <v>8936173200123</v>
+        <v>8935001234568</v>
       </c>
       <c r="E13" t="str">
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>245000</v>
+        <v>449000</v>
       </c>
       <c r="G13" t="str">
-        <v>Cocoon</v>
+        <v>Canifa</v>
       </c>
       <c r="H13" t="str">
         <v>Hoàn thành</v>
@@ -781,33 +781,468 @@
         <v>POS-2025-012</v>
       </c>
       <c r="B14" t="str">
-        <v>2025-07-06 14:25:00</v>
+        <v>2025-07-06 10:35:00</v>
       </c>
       <c r="C14" t="str">
-        <v>Sữa Rửa Mặt CeraVe Foaming Cleanser 236ml</v>
+        <v>Quần Jean Nam Slimfit Co Giãn</v>
       </c>
       <c r="D14" t="str">
+        <v>8935001234568</v>
+      </c>
+      <c r="E14" t="str">
+        <v>1</v>
+      </c>
+      <c r="F14" t="str">
+        <v>449000</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Canifa</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I14" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>POS-2025-013</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-07-07 08:45:00</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Giày Thể Thao Biti's Hunter Street</v>
+      </c>
+      <c r="D15" t="str">
+        <v>8935001234569</v>
+      </c>
+      <c r="E15" t="str">
+        <v>1</v>
+      </c>
+      <c r="F15" t="str">
+        <v>899000</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Biti's</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I15" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>POS-2025-014</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2025-07-07 11:00:00</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Áo Khoác Gió Nam Chống Thấm Nước</v>
+      </c>
+      <c r="D16" t="str">
+        <v>8935001234571</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1</v>
+      </c>
+      <c r="F16" t="str">
+        <v>699000</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Uniqlo</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I16" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>POS-2025-015</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2025-07-08 09:30:00</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Balo Laptop Chống Sốc 15.6 inch</v>
+      </c>
+      <c r="D17" t="str">
+        <v>8935001234573</v>
+      </c>
+      <c r="E17" t="str">
+        <v>1</v>
+      </c>
+      <c r="F17" t="str">
+        <v>890000</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Tomtoc</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I17" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>POS-2025-016</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2025-07-08 14:00:00</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Kính Mát Phân Cực Chống UV400</v>
+      </c>
+      <c r="D18" t="str">
+        <v>8935001234574</v>
+      </c>
+      <c r="E18" t="str">
+        <v>1</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2490000</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Rayban</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I18" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>POS-2025-017</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2025-07-09 08:15:00</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Dép Quai Ngang Adidas Adilette</v>
+      </c>
+      <c r="D19" t="str">
+        <v>8935001234575</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2</v>
+      </c>
+      <c r="F19" t="str">
+        <v>750000</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Adidas</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I19" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>POS-2025-018</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2025-07-09 10:45:00</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Nón Lưỡi Trai MLB NY Yankees</v>
+      </c>
+      <c r="D20" t="str">
+        <v>8935001234576</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>1290000</v>
+      </c>
+      <c r="G20" t="str">
+        <v>MLB</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I20" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>POS-2025-019</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2025-07-10 09:00:00</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Nồi Chiên Không Dầu Philips 4.5L HD9200</v>
+      </c>
+      <c r="D21" t="str">
+        <v>8710103856789</v>
+      </c>
+      <c r="E21" t="str">
+        <v>1</v>
+      </c>
+      <c r="F21" t="str">
+        <v>1490000</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Philips</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I21" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>POS-2025-020</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2025-07-10 11:30:00</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Ấm Siêu Tốc Inox Sunhouse 1.8L SHD1351</v>
+      </c>
+      <c r="D22" t="str">
+        <v>8935001234570</v>
+      </c>
+      <c r="E22" t="str">
+        <v>1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>0</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Sunhouse</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I22" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>POS-2025-021</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2025-07-11 08:20:00</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Tai Nghe Bluetooth Xiaomi Redmi Buds 4</v>
+      </c>
+      <c r="D23" t="str">
+        <v>6934177785678</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2</v>
+      </c>
+      <c r="F23" t="str">
+        <v>490000</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Xiaomi</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I23" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>POS-2025-022</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2025-07-11 10:00:00</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Máy Xay Sinh Tố Cầm Tay Lock&amp;Lock</v>
+      </c>
+      <c r="D24" t="str">
+        <v>8935001234572</v>
+      </c>
+      <c r="E24" t="str">
+        <v>1</v>
+      </c>
+      <c r="F24" t="str">
+        <v>550000</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Lock&amp;Lock</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I24" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>POS-2025-023</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2025-07-12 09:15:00</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Kem Chống Nắng La Roche-Posay Anthelios 50ml</v>
+      </c>
+      <c r="D25" t="str">
+        <v>3337875591079</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2</v>
+      </c>
+      <c r="F25" t="str">
+        <v>395000</v>
+      </c>
+      <c r="G25" t="str">
+        <v>La Roche-Posay</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I25" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>POS-2025-024</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2025-07-12 14:30:00</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Nước Tẩy Trang Bí Đao Cocoon 500ml</v>
+      </c>
+      <c r="D26" t="str">
+        <v>8936173200123</v>
+      </c>
+      <c r="E26" t="str">
+        <v>1</v>
+      </c>
+      <c r="F26" t="str">
+        <v>245000</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Cocoon</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I26" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>POS-2025-025</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2025-07-13 08:45:00</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Sữa Rửa Mặt Tạo Bọt CeraVe Foaming Cleanser 236ml</v>
+      </c>
+      <c r="D27" t="str">
         <v>3337875597354</v>
       </c>
-      <c r="E14" t="str">
-        <v>1</v>
-      </c>
-      <c r="F14" t="str">
+      <c r="E27" t="str">
+        <v>1</v>
+      </c>
+      <c r="F27" t="str">
         <v>320000</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G27" t="str">
         <v>CeraVe</v>
       </c>
-      <c r="H14" t="str">
+      <c r="H27" t="str">
         <v>Đã hủy</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I27" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>POS-2025-026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2025-07-13 11:00:00</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Bút Bi Thiên Long TL-027</v>
+      </c>
+      <c r="D28" t="str">
+        <v>8935001888001</v>
+      </c>
+      <c r="E28" t="str">
+        <v>10</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5000</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Thiên Long</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I28" t="str">
+        <v>POS</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>POS-2025-027</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2025-07-13 14:20:00</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Vở Kẻ Ngang Campus 200 Trang</v>
+      </c>
+      <c r="D29" t="str">
+        <v>8935001888002</v>
+      </c>
+      <c r="E29" t="str">
+        <v>5</v>
+      </c>
+      <c r="F29" t="str">
+        <v>18000</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Hoàn thành</v>
+      </c>
+      <c r="I29" t="str">
         <v>POS</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample-data/don-hang-pos-cua-hang.xlsx
+++ b/sample-data/don-hang-pos-cua-hang.xlsx
@@ -468,7 +468,7 @@
         <v>Đắc Nhân Tâm (Tái Bản 2025)</v>
       </c>
       <c r="D3" t="str">
-        <v>9786045678901</v>
+        <v>9786045678909</v>
       </c>
       <c r="E3" t="str">
         <v>2</v>
@@ -497,7 +497,7 @@
         <v>Nhà Giả Kim</v>
       </c>
       <c r="D4" t="str">
-        <v>9786045678902</v>
+        <v>9786045678916</v>
       </c>
       <c r="E4" t="str">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>Tuổi Trẻ Đáng Giá Bao Nhiêu</v>
       </c>
       <c r="D5" t="str">
-        <v>9786045678903</v>
+        <v>9786045678923</v>
       </c>
       <c r="E5" t="str">
         <v>1</v>
@@ -555,7 +555,7 @@
         <v>Cà Phê Cùng Tony</v>
       </c>
       <c r="D6" t="str">
-        <v>9786045678904</v>
+        <v>9786045678930</v>
       </c>
       <c r="E6" t="str">
         <v>2</v>
@@ -584,7 +584,7 @@
         <v>Tôi Thấy Hoa Vàng Trên Cỏ Xanh</v>
       </c>
       <c r="D7" t="str">
-        <v>9786045678905</v>
+        <v>9786045678947</v>
       </c>
       <c r="E7" t="str">
         <v>1</v>
@@ -613,7 +613,7 @@
         <v>Cho Tôi Xin Một Vé Đi Tuổi Thơ</v>
       </c>
       <c r="D8" t="str">
-        <v>9786045678906</v>
+        <v>9786045678954</v>
       </c>
       <c r="E8" t="str">
         <v>3</v>
@@ -642,7 +642,7 @@
         <v>Sapiens: Lược Sử Loài Người</v>
       </c>
       <c r="D9" t="str">
-        <v>9786045678907</v>
+        <v>9786045678961</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
@@ -671,7 +671,7 @@
         <v>Atomic Habits - Thay Đổi Tí Hon Hiệu Quả Bất Ngờ</v>
       </c>
       <c r="D10" t="str">
-        <v>9786045678908</v>
+        <v>9786045678978</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
@@ -700,7 +700,7 @@
         <v>Dám Bị Ghét</v>
       </c>
       <c r="D11" t="str">
-        <v>9786045678909</v>
+        <v>9786045678985</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
@@ -729,7 +729,7 @@
         <v>Áo Thun Nam Cotton Compact Cổ Tròn</v>
       </c>
       <c r="D12" t="str">
-        <v>8935001234567</v>
+        <v>8935001234562</v>
       </c>
       <c r="E12" t="str">
         <v>3</v>
@@ -758,7 +758,7 @@
         <v>Quần Jean Nam Slimfit Co Giãn</v>
       </c>
       <c r="D13" t="str">
-        <v>8935001234568</v>
+        <v>8935001234579</v>
       </c>
       <c r="E13" t="str">
         <v>1</v>
@@ -787,7 +787,7 @@
         <v>Quần Jean Nam Slimfit Co Giãn</v>
       </c>
       <c r="D14" t="str">
-        <v>8935001234568</v>
+        <v>8935001234579</v>
       </c>
       <c r="E14" t="str">
         <v>1</v>
@@ -816,7 +816,7 @@
         <v>Giày Thể Thao Biti's Hunter Street</v>
       </c>
       <c r="D15" t="str">
-        <v>8935001234569</v>
+        <v>8935001234586</v>
       </c>
       <c r="E15" t="str">
         <v>1</v>
@@ -845,7 +845,7 @@
         <v>Áo Khoác Gió Nam Chống Thấm Nước</v>
       </c>
       <c r="D16" t="str">
-        <v>8935001234571</v>
+        <v>8935001234593</v>
       </c>
       <c r="E16" t="str">
         <v>1</v>
@@ -874,7 +874,7 @@
         <v>Balo Laptop Chống Sốc 15.6 inch</v>
       </c>
       <c r="D17" t="str">
-        <v>8935001234573</v>
+        <v>8935001234609</v>
       </c>
       <c r="E17" t="str">
         <v>1</v>
@@ -903,7 +903,7 @@
         <v>Kính Mát Phân Cực Chống UV400</v>
       </c>
       <c r="D18" t="str">
-        <v>8935001234574</v>
+        <v>8935001234616</v>
       </c>
       <c r="E18" t="str">
         <v>1</v>
@@ -932,7 +932,7 @@
         <v>Dép Quai Ngang Adidas Adilette</v>
       </c>
       <c r="D19" t="str">
-        <v>8935001234575</v>
+        <v>8935001234623</v>
       </c>
       <c r="E19" t="str">
         <v>2</v>
@@ -961,7 +961,7 @@
         <v>Nón Lưỡi Trai MLB NY Yankees</v>
       </c>
       <c r="D20" t="str">
-        <v>8935001234576</v>
+        <v>8935001234630</v>
       </c>
       <c r="E20" t="str">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>Nồi Chiên Không Dầu Philips 4.5L HD9200</v>
       </c>
       <c r="D21" t="str">
-        <v>8710103856789</v>
+        <v>8710103856788</v>
       </c>
       <c r="E21" t="str">
         <v>1</v>
@@ -1019,7 +1019,7 @@
         <v>Ấm Siêu Tốc Inox Sunhouse 1.8L SHD1351</v>
       </c>
       <c r="D22" t="str">
-        <v>8935001234570</v>
+        <v>8935001234647</v>
       </c>
       <c r="E22" t="str">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>Tai Nghe Bluetooth Xiaomi Redmi Buds 4</v>
       </c>
       <c r="D23" t="str">
-        <v>6934177785678</v>
+        <v>6934177785672</v>
       </c>
       <c r="E23" t="str">
         <v>2</v>
@@ -1077,7 +1077,7 @@
         <v>Máy Xay Sinh Tố Cầm Tay Lock&amp;Lock</v>
       </c>
       <c r="D24" t="str">
-        <v>8935001234572</v>
+        <v>8935001234654</v>
       </c>
       <c r="E24" t="str">
         <v>1</v>
@@ -1106,7 +1106,7 @@
         <v>Kem Chống Nắng La Roche-Posay Anthelios 50ml</v>
       </c>
       <c r="D25" t="str">
-        <v>3337875591079</v>
+        <v>3337875591072</v>
       </c>
       <c r="E25" t="str">
         <v>2</v>
@@ -1135,7 +1135,7 @@
         <v>Nước Tẩy Trang Bí Đao Cocoon 500ml</v>
       </c>
       <c r="D26" t="str">
-        <v>8936173200123</v>
+        <v>8936173200126</v>
       </c>
       <c r="E26" t="str">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>Sữa Rửa Mặt Tạo Bọt CeraVe Foaming Cleanser 236ml</v>
       </c>
       <c r="D27" t="str">
-        <v>3337875597354</v>
+        <v>3337875597357</v>
       </c>
       <c r="E27" t="str">
         <v>1</v>
@@ -1193,7 +1193,7 @@
         <v>Bút Bi Thiên Long TL-027</v>
       </c>
       <c r="D28" t="str">
-        <v>8935001888001</v>
+        <v>8935001888005</v>
       </c>
       <c r="E28" t="str">
         <v>10</v>
@@ -1222,7 +1222,7 @@
         <v>Vở Kẻ Ngang Campus 200 Trang</v>
       </c>
       <c r="D29" t="str">
-        <v>8935001888002</v>
+        <v>8935001888012</v>
       </c>
       <c r="E29" t="str">
         <v>5</v>
